--- a/data/trans_camb/P6907S1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 12,42</t>
+          <t>-9,02; 13,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,16; 0,43</t>
+          <t>-14,23; 0,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 19,6</t>
+          <t>-5,11; 18,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 0,0</t>
+          <t>-18,36; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 5,36</t>
+          <t>-15,51; 5,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 3,16</t>
+          <t>-16,02; 3,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 7,16</t>
+          <t>-9,8; 6,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 0,49</t>
+          <t>-12,25; -0,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 8,48</t>
+          <t>-6,54; 9,85</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 326,64</t>
+          <t>-100,0; 318,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 142,82</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-52,32; 436,56</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-50,06; 433,92</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-85,49; 180,68</t>
+          <t>-100,0; 157,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 68,91</t>
+          <t>-100,0; 49,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 182,44</t>
+          <t>-59,89; 206,53</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-14,29; 7,6</t>
+          <t>-13,78; 6,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -2,5</t>
+          <t>-15,85; -2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 9,7</t>
+          <t>-7,82; 10,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-22,6; -4,13</t>
+          <t>-24,35; -5,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 5,22</t>
+          <t>-17,99; 4,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,93; 2,19</t>
+          <t>-18,48; 2,4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,25; -0,74</t>
+          <t>-14,27; -0,68</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-13,67; -1,3</t>
+          <t>-14,71; -2,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 3,43</t>
+          <t>-8,98; 3,93</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 119,09</t>
+          <t>-100,0; 106,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -11,06</t>
+          <t>-94,06; -8,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-49,68; 127,91</t>
+          <t>-50,61; 126,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 110,89</t>
+          <t>-100,0; 125,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-86,21; 55,02</t>
+          <t>-83,02; 92,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,77</t>
+          <t>-100,0; 10,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-86,81; -0,3</t>
+          <t>-90,11; -9,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 47,93</t>
+          <t>-57,63; 48,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,38; 6,98</t>
+          <t>-11,11; 5,89</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,07; 1,08</t>
+          <t>-12,39; 0,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 11,44</t>
+          <t>-7,31; 11,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,86; 4,46</t>
+          <t>-14,89; 4,42</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,33; -2,06</t>
+          <t>-19,11; -2,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 15,98</t>
+          <t>-12,15; 17,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 3,05</t>
+          <t>-10,36; 2,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,12; -1,8</t>
+          <t>-12,08; -1,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,61; 12,35</t>
+          <t>-4,99; 11,62</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 309,59</t>
+          <t>-100,0; 240,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-96,7; 106,67</t>
+          <t>-100,0; 72,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-87,5; 284,51</t>
+          <t>-76,67; 319,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,03; 384,53</t>
+          <t>-67,58; 404,29</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 94,39</t>
+          <t>-100,0; 79,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,55; -18,74</t>
+          <t>-95,19; -7,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-43,03; 239,91</t>
+          <t>-44,86; 236,8</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,39; 4,63</t>
+          <t>-10,42; 3,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 3,89</t>
+          <t>-8,47; 3,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 7,28</t>
+          <t>-7,23; 7,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,8; 8,77</t>
+          <t>-15,98; 7,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,2; -4,21</t>
+          <t>-20,81; -4,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,72; 5,89</t>
+          <t>-12,51; 4,52</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-11,02; 2,53</t>
+          <t>-10,58; 2,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -0,91</t>
+          <t>-10,93; -0,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 3,98</t>
+          <t>-6,32; 4,17</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 123,45</t>
+          <t>-100,0; 139,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-81,53; 70,5</t>
+          <t>-82,63; 85,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-63,84; 136,3</t>
+          <t>-65,96; 147,36</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,38</t>
+          <t>-100,0; 129,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -5,15</t>
+          <t>-100,0; -7,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-68,34; 87,52</t>
+          <t>-69,59; 58,56</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,67; 56,47</t>
+          <t>-87,77; 42,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-85,77; -4,98</t>
+          <t>-85,26; 0,14</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,12; 58,55</t>
+          <t>-51,09; 63,35</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,97; 1,05</t>
+          <t>-8,15; 1,01</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,31; -2,52</t>
+          <t>-9,37; -2,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 7,02</t>
+          <t>-2,54; 6,79</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-12,91; -2,21</t>
+          <t>-13,33; -2,67</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,12; -3,75</t>
+          <t>-13,36; -4,09</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,75</t>
+          <t>-7,6; 2,37</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,94; -1,63</t>
+          <t>-8,81; -1,36</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -4,08</t>
+          <t>-9,4; -4,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 3,34</t>
+          <t>-3,55; 3,33</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-74,55; 20,46</t>
+          <t>-75,87; 17,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-80,42; -29,97</t>
+          <t>-82,47; -29,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,32; 106,95</t>
+          <t>-23,83; 92,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-92,52; -9,92</t>
+          <t>-100,0; -19,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-93,29; -43,66</t>
+          <t>-93,2; -45,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,82; 35,67</t>
+          <t>-54,89; 31,19</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-78,78; -15,37</t>
+          <t>-77,5; -14,71</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,76; -47,87</t>
+          <t>-81,84; -44,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-33,17; 39,87</t>
+          <t>-31,26; 45,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P6907S1-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P6907S1-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>4,24</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,95</t>
+          <t>-3,11</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,49</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 13,19</t>
+          <t>-10,4; 12,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,23; 0,51</t>
+          <t>-14,61; 0,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 18,31</t>
+          <t>-5,81; 19,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-18,36; 0,0</t>
+          <t>-18,44; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,51; 5,14</t>
+          <t>-14,82; 5,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,02; 3,31</t>
+          <t>-15,64; 2,52</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 6,37</t>
+          <t>-9,14; 8,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,25; -0,07</t>
+          <t>-11,22; 0,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 9,85</t>
+          <t>-6,46; 9,12</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>47,66%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-51,5%</t>
+          <t>-54,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>6,14%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 318,59</t>
+          <t>-100,0; 254,13</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 142,82</t>
+          <t>-100,0; 97,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-52,32; 436,56</t>
+          <t>-54,59; 396,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 157,35</t>
+          <t>-100,0; 206,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,25</t>
+          <t>-100,0; 124,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-59,89; 206,53</t>
+          <t>-62,3; 199,76</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1,02</t>
+          <t>-1,01</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-6,33</t>
+          <t>-6,56</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-3,48</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 6,17</t>
+          <t>-14,04; 7,06</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,85; -2,28</t>
+          <t>-16,04; -2,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 10,0</t>
+          <t>-9,24; 7,43</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,35; -5,66</t>
+          <t>-24,59; -5,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,99; 4,92</t>
+          <t>-16,43; 5,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 2,4</t>
+          <t>-17,98; 1,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,27; -0,68</t>
+          <t>-14,52; -0,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-14,71; -2,04</t>
+          <t>-13,38; -1,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 3,93</t>
+          <t>-9,21; 2,44</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>-8,52%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-53,2%</t>
+          <t>-55,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-20,35%</t>
+          <t>-29,37%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 106,42</t>
+          <t>-100,0; 129,76</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-94,06; -8,99</t>
+          <t>-93,76; -6,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-50,61; 126,62</t>
+          <t>-57,78; 102,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,27 +1019,27 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 125,5</t>
+          <t>-90,11; 160,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,02; 92,43</t>
+          <t>-85,2; 45,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 10,16</t>
+          <t>-100,0; 0,43</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-90,11; -9,95</t>
+          <t>-85,58; -5,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-57,63; 48,16</t>
+          <t>-61,0; 29,66</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,98</t>
+          <t>2,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,33</t>
+          <t>10,36</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>6,68</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 5,89</t>
+          <t>-10,2; 7,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 0,52</t>
+          <t>-12,55; 0,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 11,75</t>
+          <t>-5,74; 14,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-14,89; 4,42</t>
+          <t>-14,59; 5,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,11; -2,05</t>
+          <t>-19,06; -2,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 17,32</t>
+          <t>-1,17; 22,64</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 2,74</t>
+          <t>-9,97; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-12,08; -1,96</t>
+          <t>-11,97; -1,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 11,62</t>
+          <t>-0,6; 15,08</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>125,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 240,88</t>
+          <t>-100,0; 267,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 72,07</t>
+          <t>-100,0; 42,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-76,67; 319,33</t>
+          <t>-70,66; 373,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,58; 404,29</t>
+          <t>-25,43; 803,94</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 79,25</t>
+          <t>-100,0; 91,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-95,19; -7,8</t>
+          <t>-100,0; -21,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-44,86; 236,8</t>
+          <t>-15,65; 287,01</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0,22</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,89</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,27</t>
+          <t>-0,87</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 3,79</t>
+          <t>-9,87; 5,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 3,36</t>
+          <t>-8,61; 4,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 7,0</t>
+          <t>-7,27; 6,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,98; 7,55</t>
+          <t>-15,72; 6,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -4,73</t>
+          <t>-20,55; -4,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 4,52</t>
+          <t>-11,45; 7,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,58; 2,42</t>
+          <t>-10,29; 2,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -0,64</t>
+          <t>-10,98; -0,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,17</t>
+          <t>-6,15; 4,81</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>-3,68%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,57%</t>
+          <t>-19,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-12,7%</t>
+          <t>-8,7%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 139,18</t>
+          <t>-100,0; 163,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-82,63; 85,11</t>
+          <t>-83,95; 95,87</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,96; 147,36</t>
+          <t>-70,43; 134,01</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 129,57</t>
+          <t>-100,0; 118,22</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,96</t>
+          <t>-100,0; 3,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,59; 58,56</t>
+          <t>-60,03; 102,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,77; 42,28</t>
+          <t>-87,18; 45,65</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-85,26; 0,14</t>
+          <t>-85,84; -5,24</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-51,09; 63,35</t>
+          <t>-48,89; 63,86</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,62</t>
+          <t>1,05</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,59</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,24</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-8,15; 1,01</t>
+          <t>-8,19; 1,67</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-9,37; -2,5</t>
+          <t>-9,23; -2,09</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 6,79</t>
+          <t>-3,06; 6,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,67</t>
+          <t>-12,88; -2,73</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,36; -4,09</t>
+          <t>-13,14; -3,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 2,37</t>
+          <t>-6,69; 3,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-8,81; -1,36</t>
+          <t>-8,22; -1,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,4; -4,12</t>
+          <t>-9,66; -4,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 3,33</t>
+          <t>-3,55; 3,13</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-24,15%</t>
+          <t>-14,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-2,45%</t>
+          <t>0,76%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-75,87; 17,28</t>
+          <t>-74,98; 30,74</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-82,47; -29,69</t>
+          <t>-81,96; -27,42</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,83; 92,94</t>
+          <t>-29,31; 88,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -19,6</t>
+          <t>-93,37; -20,83</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-93,2; -45,35</t>
+          <t>-92,99; -43,82</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-54,89; 31,19</t>
+          <t>-47,2; 56,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-77,5; -14,71</t>
+          <t>-76,33; -17,21</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-81,84; -44,51</t>
+          <t>-81,41; -46,05</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 45,57</t>
+          <t>-31,36; 37,43</t>
         </is>
       </c>
     </row>
